--- a/Output/logit_marginal_effects_glm_cluster_se_stata.xlsx
+++ b/Output/logit_marginal_effects_glm_cluster_se_stata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="499" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="453" uniqueCount="106">
   <si>
     <t>spec</t>
   </si>
@@ -80,16 +80,16 @@
     <t>ame_formatted</t>
   </si>
   <si>
-    <t>1.207 (2.739)</t>
-  </si>
-  <si>
-    <t>2.268 (9.429)</t>
-  </si>
-  <si>
-    <t>1.304 (2.827)</t>
-  </si>
-  <si>
-    <t>2.405 (9.832)</t>
+    <t>0.012 (0.027)</t>
+  </si>
+  <si>
+    <t>0.023 (0.094)</t>
+  </si>
+  <si>
+    <t>0.013 (0.028)</t>
+  </si>
+  <si>
+    <t>0.024 (0.098)</t>
   </si>
   <si>
     <t>no_controls_ame</t>
@@ -107,112 +107,79 @@
     <t>variable</t>
   </si>
   <si>
-    <t>pre_age</t>
-  </si>
-  <si>
-    <t>pre_male</t>
-  </si>
-  <si>
-    <t>popdensgeo2</t>
-  </si>
-  <si>
-    <t>pre_unemp</t>
-  </si>
-  <si>
-    <t>pre_partner</t>
-  </si>
-  <si>
-    <t>pre_educ</t>
-  </si>
-  <si>
-    <t>pre_lr</t>
-  </si>
-  <si>
-    <t>pre_polint</t>
-  </si>
-  <si>
-    <t>pre_blank</t>
-  </si>
-  <si>
-    <t>Mean age</t>
-  </si>
-  <si>
-    <t>Share male</t>
-  </si>
-  <si>
-    <t>Log population density</t>
+    <t>popdensgeo2_2010</t>
+  </si>
+  <si>
+    <t>share_female_2010</t>
+  </si>
+  <si>
+    <t>mean_yrschool_2010</t>
+  </si>
+  <si>
+    <t>median_age_2010</t>
+  </si>
+  <si>
+    <t>share_laborforce_2010</t>
+  </si>
+  <si>
+    <t>share_unemployed_2010</t>
+  </si>
+  <si>
+    <t>share_izq_amplia_pre_avg</t>
+  </si>
+  <si>
+    <t>share_alt_pre_avg</t>
+  </si>
+  <si>
+    <t>Population density</t>
+  </si>
+  <si>
+    <t>Female population share</t>
+  </si>
+  <si>
+    <t>Mean years of education</t>
+  </si>
+  <si>
+    <t>Median age</t>
+  </si>
+  <si>
+    <t>Share in labor force</t>
   </si>
   <si>
     <t>Share unemployed</t>
   </si>
   <si>
-    <t>Share partnered</t>
-  </si>
-  <si>
-    <t>Mean years of education</t>
-  </si>
-  <si>
-    <t>Mean left-right ideology</t>
-  </si>
-  <si>
-    <t>Share very interested in politics</t>
-  </si>
-  <si>
-    <t>Share blank/null vote</t>
-  </si>
-  <si>
-    <t>0.914 (0.801)</t>
-  </si>
-  <si>
-    <t>0.636 (0.834)</t>
-  </si>
-  <si>
-    <t>40.633 (82.103)</t>
-  </si>
-  <si>
-    <t>51.566 (85.224)</t>
-  </si>
-  <si>
-    <t>-0.089 (0.325)</t>
-  </si>
-  <si>
-    <t>-0.078 (0.335)</t>
-  </si>
-  <si>
-    <t>48.640 (33.944)</t>
-  </si>
-  <si>
-    <t>41.971 (34.877)</t>
-  </si>
-  <si>
-    <t>0.483 (14.244)</t>
-  </si>
-  <si>
-    <t>-2.533 (13.739)</t>
-  </si>
-  <si>
-    <t>-0.487 (0.880)</t>
-  </si>
-  <si>
-    <t>-0.349 (0.900)</t>
-  </si>
-  <si>
-    <t>-4.242*** (1.457)</t>
-  </si>
-  <si>
-    <t>-4.548*** (1.533)</t>
-  </si>
-  <si>
-    <t>22.676 (15.968)</t>
-  </si>
-  <si>
-    <t>21.191 (16.159)</t>
-  </si>
-  <si>
-    <t>-8.129 (21.087)</t>
-  </si>
-  <si>
-    <t>-5.527 (21.201)</t>
+    <t>Left vote share</t>
+  </si>
+  <si>
+    <t>Ideological alternation</t>
+  </si>
+  <si>
+    <t>0.000 (0.000)</t>
+  </si>
+  <si>
+    <t>-0.003 (0.006)</t>
+  </si>
+  <si>
+    <t>0.002 (0.007)</t>
+  </si>
+  <si>
+    <t>0.001 (0.007)</t>
+  </si>
+  <si>
+    <t>0.002 (0.003)</t>
+  </si>
+  <si>
+    <t>0.002 (0.002)</t>
+  </si>
+  <si>
+    <t>-0.011 (0.010)</t>
+  </si>
+  <si>
+    <t>-0.010 (0.010)</t>
+  </si>
+  <si>
+    <t>-0.000 (0.001)</t>
   </si>
   <si>
     <t>variable_label</t>
@@ -227,58 +194,52 @@
     <t>share_1956_1978</t>
   </si>
   <si>
-    <t>pxs36_pre_age</t>
-  </si>
-  <si>
-    <t>pxs56_pre_age</t>
-  </si>
-  <si>
-    <t>pxs36_pre_male</t>
-  </si>
-  <si>
-    <t>pxs56_pre_male</t>
-  </si>
-  <si>
-    <t>pxs36_popdensgeo2</t>
-  </si>
-  <si>
-    <t>pxs56_popdensgeo2</t>
-  </si>
-  <si>
-    <t>pxs36_pre_unemp</t>
-  </si>
-  <si>
-    <t>pxs56_pre_unemp</t>
-  </si>
-  <si>
-    <t>pxs36_pre_partner</t>
-  </si>
-  <si>
-    <t>pxs56_pre_partner</t>
-  </si>
-  <si>
-    <t>pxs36_pre_educ</t>
-  </si>
-  <si>
-    <t>pxs56_pre_educ</t>
-  </si>
-  <si>
-    <t>pxs36_pre_lr</t>
-  </si>
-  <si>
-    <t>pxs56_pre_lr</t>
-  </si>
-  <si>
-    <t>pxs36_pre_polint</t>
-  </si>
-  <si>
-    <t>pxs56_pre_polint</t>
-  </si>
-  <si>
-    <t>pxs36_pre_blank</t>
-  </si>
-  <si>
-    <t>pxs56_pre_blank</t>
+    <t>pxs36_popdensgeo2_2010</t>
+  </si>
+  <si>
+    <t>pxs56_popdensgeo2_2010</t>
+  </si>
+  <si>
+    <t>pxs36_share_female_2010</t>
+  </si>
+  <si>
+    <t>pxs56_share_female_2010</t>
+  </si>
+  <si>
+    <t>pxs36_mean_yrschool_2010</t>
+  </si>
+  <si>
+    <t>pxs56_mean_yrschool_2010</t>
+  </si>
+  <si>
+    <t>pxs36_median_age_2010</t>
+  </si>
+  <si>
+    <t>pxs56_median_age_2010</t>
+  </si>
+  <si>
+    <t>pxs36_share_laborforce_2010</t>
+  </si>
+  <si>
+    <t>pxs56_share_laborforce_2010</t>
+  </si>
+  <si>
+    <t>pxs36_share_unemployed_2010</t>
+  </si>
+  <si>
+    <t>pxs56_share_unemployed_2010</t>
+  </si>
+  <si>
+    <t>pxs36_share_izq_amplia_pre_avg</t>
+  </si>
+  <si>
+    <t>pxs56_share_izq_amplia_pre_avg</t>
+  </si>
+  <si>
+    <t>pxs36_share_alt_pre_avg</t>
+  </si>
+  <si>
+    <t>pxs56_share_alt_pre_avg</t>
   </si>
   <si>
     <t>\(Post \times X \times Share_{1936-1955}\)</t>
@@ -287,112 +248,82 @@
     <t>\(Post \times X \times Share_{1956-1978}\)</t>
   </si>
   <si>
-    <t>0.165 (2.554)</t>
-  </si>
-  <si>
-    <t>-11.219 (9.708)</t>
-  </si>
-  <si>
-    <t>2.214 (2.920)</t>
-  </si>
-  <si>
-    <t>-19.855* (11.751)</t>
-  </si>
-  <si>
-    <t>194.417 (175.475)</t>
-  </si>
-  <si>
-    <t>-685.175 (755.223)</t>
-  </si>
-  <si>
-    <t>372.046 (235.155)</t>
-  </si>
-  <si>
-    <t>-1084.751 (1017.948)</t>
-  </si>
-  <si>
-    <t>0.269 (0.965)</t>
-  </si>
-  <si>
-    <t>-3.465 (3.283)</t>
-  </si>
-  <si>
-    <t>-0.072 (1.135)</t>
-  </si>
-  <si>
-    <t>-3.088 (4.001)</t>
-  </si>
-  <si>
-    <t>122.881 (123.233)</t>
-  </si>
-  <si>
-    <t>-82.700 (469.756)</t>
-  </si>
-  <si>
-    <t>218.586* (115.817)</t>
-  </si>
-  <si>
-    <t>-440.506 (495.232)</t>
-  </si>
-  <si>
-    <t>-63.137** (30.760)</t>
-  </si>
-  <si>
-    <t>219.015** (107.636)</t>
-  </si>
-  <si>
-    <t>-73.256*** (26.996)</t>
-  </si>
-  <si>
-    <t>259.182** (114.434)</t>
-  </si>
-  <si>
-    <t>-1.162 (2.477)</t>
-  </si>
-  <si>
-    <t>-7.316 (9.702)</t>
-  </si>
-  <si>
-    <t>-2.605 (2.445)</t>
-  </si>
-  <si>
-    <t>-6.844 (9.421)</t>
-  </si>
-  <si>
-    <t>-2.292 (9.224)</t>
-  </si>
-  <si>
-    <t>11.304 (26.968)</t>
-  </si>
-  <si>
-    <t>-0.500 (9.884)</t>
-  </si>
-  <si>
-    <t>0.834 (31.785)</t>
-  </si>
-  <si>
-    <t>-46.744 (43.691)</t>
-  </si>
-  <si>
-    <t>-172.496 (145.679)</t>
-  </si>
-  <si>
-    <t>-45.902 (42.072)</t>
-  </si>
-  <si>
-    <t>-252.789* (142.095)</t>
-  </si>
-  <si>
-    <t>0.101 (98.150)</t>
-  </si>
-  <si>
-    <t>203.155 (419.876)</t>
-  </si>
-  <si>
-    <t>25.546 (100.055)</t>
-  </si>
-  <si>
-    <t>146.897 (394.224)</t>
+    <t>-0.000 (0.000)</t>
+  </si>
+  <si>
+    <t>-0.022 (0.021)</t>
+  </si>
+  <si>
+    <t>0.038 (0.083)</t>
+  </si>
+  <si>
+    <t>-0.050** (0.023)</t>
+  </si>
+  <si>
+    <t>0.102 (0.105)</t>
+  </si>
+  <si>
+    <t>-0.010 (0.025)</t>
+  </si>
+  <si>
+    <t>-0.047 (0.089)</t>
+  </si>
+  <si>
+    <t>-0.030 (0.028)</t>
+  </si>
+  <si>
+    <t>0.008 (0.136)</t>
+  </si>
+  <si>
+    <t>0.002 (0.008)</t>
+  </si>
+  <si>
+    <t>-0.046 (0.033)</t>
+  </si>
+  <si>
+    <t>-0.001 (0.008)</t>
+  </si>
+  <si>
+    <t>-0.032 (0.043)</t>
+  </si>
+  <si>
+    <t>-0.002 (0.005)</t>
+  </si>
+  <si>
+    <t>-0.026* (0.016)</t>
+  </si>
+  <si>
+    <t>-0.026 (0.026)</t>
+  </si>
+  <si>
+    <t>-0.037 (0.027)</t>
+  </si>
+  <si>
+    <t>0.196** (0.096)</t>
+  </si>
+  <si>
+    <t>-0.020 (0.041)</t>
+  </si>
+  <si>
+    <t>0.090 (0.168)</t>
+  </si>
+  <si>
+    <t>-0.000 (0.002)</t>
+  </si>
+  <si>
+    <t>0.003 (0.007)</t>
+  </si>
+  <si>
+    <t>0.001 (0.001)</t>
+  </si>
+  <si>
+    <t>-0.003 (0.003)</t>
+  </si>
+  <si>
+    <t>-0.001 (0.001)</t>
+  </si>
+  <si>
+    <t>0.003 (0.005)</t>
   </si>
   <si>
     <t>no_controls_1936_1955</t>
@@ -505,7 +436,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0120678363985389</v>
+        <v>0.0120678363985386</v>
       </c>
       <c r="F2" s="1">
         <v>0.027386970818042755</v>
@@ -514,10 +445,10 @@
         <v>0.6594725251197815</v>
       </c>
       <c r="H2" s="1">
-        <v>1.206783652305603</v>
+        <v>0.012067836709320545</v>
       </c>
       <c r="I2" s="1">
-        <v>2.7386970520019531</v>
+        <v>0.027386970818042755</v>
       </c>
       <c r="J2" s="1">
         <v>7503</v>
@@ -543,7 +474,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1">
-        <v>0.022682625850490901</v>
+        <v>0.022682625850491901</v>
       </c>
       <c r="F3" s="1">
         <v>0.094286225736141205</v>
@@ -552,10 +483,10 @@
         <v>0.8098868727684021</v>
       </c>
       <c r="H3" s="1">
-        <v>2.2682626247406006</v>
+        <v>0.02268262580037117</v>
       </c>
       <c r="I3" s="1">
-        <v>9.4286231994628906</v>
+        <v>0.094286225736141205</v>
       </c>
       <c r="J3" s="1">
         <v>7503</v>
@@ -581,7 +512,7 @@
         <v>10</v>
       </c>
       <c r="E4" s="1">
-        <v>0.0130359826943575</v>
+        <v>0.013035982694357399</v>
       </c>
       <c r="F4" s="1">
         <v>0.028266821056604385</v>
@@ -590,10 +521,10 @@
         <v>0.64467227458953857</v>
       </c>
       <c r="H4" s="1">
-        <v>1.3035982847213745</v>
+        <v>0.013035982847213745</v>
       </c>
       <c r="I4" s="1">
-        <v>2.8266820907592774</v>
+        <v>0.028266821056604385</v>
       </c>
       <c r="J4" s="1">
         <v>7448</v>
@@ -619,7 +550,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="1">
-        <v>0.024047109309971899</v>
+        <v>0.024047109309972</v>
       </c>
       <c r="F5" s="1">
         <v>0.098315641283988953</v>
@@ -628,10 +559,10 @@
         <v>0.80677324533462525</v>
       </c>
       <c r="H5" s="1">
-        <v>2.4047110080718994</v>
+        <v>0.024047110229730606</v>
       </c>
       <c r="I5" s="1">
-        <v>9.8315649032592773</v>
+        <v>0.098315641283988953</v>
       </c>
       <c r="J5" s="1">
         <v>7448</v>
@@ -718,7 +649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -761,34 +692,34 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="1">
-        <v>0.0091380930925842006</v>
+        <v>3.4549361218099999e-08</v>
       </c>
       <c r="E2" s="1">
-        <v>0.0080096423625946045</v>
+        <v>1.3250185020297067e-06</v>
       </c>
       <c r="F2" s="1">
-        <v>0.25391712784767151</v>
+        <v>0.97919780015945435</v>
       </c>
       <c r="G2" s="1">
-        <v>0.91380929946899414</v>
+        <v>3.4549362482039214e-08</v>
       </c>
       <c r="H2" s="1">
-        <v>0.80096417665481567</v>
+        <v>1.3250185020297067e-06</v>
       </c>
       <c r="I2" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="J2" s="1">
-        <v>0.0503834225272747</v>
+        <v>0.050124944904120797</v>
       </c>
       <c r="K2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -796,34 +727,34 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1">
-        <v>0.0063590231250678</v>
+        <v>1.92816416223e-07</v>
       </c>
       <c r="E3" s="1">
-        <v>0.0083366939797997475</v>
+        <v>1.3653865380547359e-06</v>
       </c>
       <c r="F3" s="1">
-        <v>0.44559752941131592</v>
+        <v>0.88769817352294922</v>
       </c>
       <c r="G3" s="1">
-        <v>0.6359022855758667</v>
+        <v>1.9281641527868487e-07</v>
       </c>
       <c r="H3" s="1">
-        <v>0.83366942405700684</v>
+        <v>1.3653865380547359e-06</v>
       </c>
       <c r="I3" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="J3" s="1">
-        <v>0.13664587667233461</v>
+        <v>0.1367599431570222</v>
       </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -831,34 +762,34 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="1">
-        <v>0.40632834793069472</v>
+        <v>-0.0029387895022474002</v>
       </c>
       <c r="E4" s="1">
-        <v>0.82102924585342407</v>
+        <v>0.0058975443243980408</v>
       </c>
       <c r="F4" s="1">
-        <v>0.6206699013710022</v>
+        <v>0.61826741695404053</v>
       </c>
       <c r="G4" s="1">
-        <v>40.632835388183594</v>
+        <v>-0.0029387895483523607</v>
       </c>
       <c r="H4" s="1">
-        <v>82.102928161621094</v>
+        <v>0.0058975443243980408</v>
       </c>
       <c r="I4" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="J4" s="1">
-        <v>0.050240198533893797</v>
+        <v>0.050150810558222299</v>
       </c>
       <c r="K4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
@@ -866,34 +797,34 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="1">
-        <v>0.51566295626716197</v>
+        <v>-0.0033704398773716998</v>
       </c>
       <c r="E5" s="1">
-        <v>0.85223895311355591</v>
+        <v>0.0057648066431283951</v>
       </c>
       <c r="F5" s="1">
-        <v>0.54513347148895264</v>
+        <v>0.55877774953842163</v>
       </c>
       <c r="G5" s="1">
-        <v>51.566295623779297</v>
+        <v>-0.0033704398665577173</v>
       </c>
       <c r="H5" s="1">
-        <v>85.223899841308594</v>
+        <v>0.0057648066431283951</v>
       </c>
       <c r="I5" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="J5" s="1">
-        <v>0.13661891543949481</v>
+        <v>0.13679505631072381</v>
       </c>
       <c r="K5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -901,34 +832,34 @@
         <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="1">
-        <v>-0.00089379831102189998</v>
+        <v>0.0019458872252735</v>
       </c>
       <c r="E6" s="1">
-        <v>0.0032547884620726109</v>
+        <v>0.007302439771592617</v>
       </c>
       <c r="F6" s="1">
-        <v>0.78361570835113525</v>
+        <v>0.78987663984298706</v>
       </c>
       <c r="G6" s="1">
-        <v>-0.089379832148551941</v>
+        <v>0.0019458872266113758</v>
       </c>
       <c r="H6" s="1">
-        <v>0.32547885179519653</v>
+        <v>0.007302439771592617</v>
       </c>
       <c r="I6" s="1">
         <v>7503</v>
       </c>
       <c r="J6" s="1">
-        <v>0.050134007096164002</v>
+        <v>0.050134593733460103</v>
       </c>
       <c r="K6" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
@@ -936,34 +867,34 @@
         <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>5</v>
       </c>
       <c r="D7" s="1">
-        <v>-0.00077722537970960001</v>
+        <v>0.00075521580839280002</v>
       </c>
       <c r="E7" s="1">
-        <v>0.0033488178160041571</v>
+        <v>0.007140173576772213</v>
       </c>
       <c r="F7" s="1">
-        <v>0.81646853685379028</v>
+        <v>0.91576486825942993</v>
       </c>
       <c r="G7" s="1">
-        <v>-0.077722534537315369</v>
+        <v>0.0007552158203907311</v>
       </c>
       <c r="H7" s="1">
-        <v>0.33488178253173828</v>
+        <v>0.007140173576772213</v>
       </c>
       <c r="I7" s="1">
         <v>7448</v>
       </c>
       <c r="J7" s="1">
-        <v>0.13676598936322959</v>
+        <v>0.13676013555637201</v>
       </c>
       <c r="K7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -971,34 +902,34 @@
         <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="1">
-        <v>0.48639905122168048</v>
+        <v>0.0021942139198655999</v>
       </c>
       <c r="E8" s="1">
-        <v>0.33943966031074524</v>
+        <v>0.0025153765454888344</v>
       </c>
       <c r="F8" s="1">
-        <v>0.15187297761440277</v>
+        <v>0.38303372263908386</v>
       </c>
       <c r="G8" s="1">
-        <v>48.639904022216797</v>
+        <v>0.0021942139137536287</v>
       </c>
       <c r="H8" s="1">
-        <v>33.943965911865234</v>
+        <v>0.0025153765454888344</v>
       </c>
       <c r="I8" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="J8" s="1">
-        <v>0.050507434580709103</v>
+        <v>0.050240969513996897</v>
       </c>
       <c r="K8" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
@@ -1006,34 +937,34 @@
         <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="1">
-        <v>0.41971055974644028</v>
+        <v>0.0021345311077266001</v>
       </c>
       <c r="E9" s="1">
-        <v>0.34876865148544312</v>
+        <v>0.0024922958109527826</v>
       </c>
       <c r="F9" s="1">
-        <v>0.22881893813610077</v>
+        <v>0.39174795150756836</v>
       </c>
       <c r="G9" s="1">
-        <v>41.971054077148438</v>
+        <v>0.0021345310378819704</v>
       </c>
       <c r="H9" s="1">
-        <v>34.876865386962891</v>
+        <v>0.0024922958109527826</v>
       </c>
       <c r="I9" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="J9" s="1">
-        <v>0.13679867622453981</v>
+        <v>0.13687482894576511</v>
       </c>
       <c r="K9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -1041,34 +972,34 @@
         <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
       <c r="D10" s="1">
-        <v>0.004834868354671</v>
+        <v>0.0022007445234024999</v>
       </c>
       <c r="E10" s="1">
-        <v>0.14243790507316589</v>
+        <v>0.0015218897024169564</v>
       </c>
       <c r="F10" s="1">
-        <v>0.97292202711105347</v>
+        <v>0.14816026389598847</v>
       </c>
       <c r="G10" s="1">
-        <v>0.48348683118820191</v>
+        <v>0.0022007445804774761</v>
       </c>
       <c r="H10" s="1">
-        <v>14.243790626525879</v>
+        <v>0.0015218897024169564</v>
       </c>
       <c r="I10" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="J10" s="1">
-        <v>0.050200842394360103</v>
+        <v>0.0503099461480696</v>
       </c>
       <c r="K10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1076,34 +1007,34 @@
         <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
       </c>
       <c r="D11" s="1">
-        <v>-0.025328159306627001</v>
+        <v>0.0022032895599430999</v>
       </c>
       <c r="E11" s="1">
-        <v>0.13739490509033203</v>
+        <v>0.0015389664331451058</v>
       </c>
       <c r="F11" s="1">
-        <v>0.85374224185943604</v>
+        <v>0.15223875641822815</v>
       </c>
       <c r="G11" s="1">
-        <v>-2.5328159332275391</v>
+        <v>0.0022032896522432566</v>
       </c>
       <c r="H11" s="1">
-        <v>13.739489555358887</v>
+        <v>0.0015389664331451058</v>
       </c>
       <c r="I11" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="J11" s="1">
-        <v>0.136555904330664</v>
+        <v>0.1369585778016342</v>
       </c>
       <c r="K11" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -1111,34 +1042,34 @@
         <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="1">
-        <v>-0.0048671244292653</v>
+        <v>-0.010550354156588801</v>
       </c>
       <c r="E12" s="1">
-        <v>0.0087985657155513764</v>
+        <v>0.010371818207204342</v>
       </c>
       <c r="F12" s="1">
-        <v>0.58014529943466187</v>
+        <v>0.30905184149742126</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.48671245574951172</v>
+        <v>-0.010550354607403278</v>
       </c>
       <c r="H12" s="1">
-        <v>0.87985652685165405</v>
+        <v>0.010371818207204342</v>
       </c>
       <c r="I12" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="J12" s="1">
-        <v>0.050248519627192997</v>
+        <v>0.050267954051078999</v>
       </c>
       <c r="K12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -1146,34 +1077,34 @@
         <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
       </c>
       <c r="D13" s="1">
-        <v>-0.0034896913046524002</v>
+        <v>-0.010100576790266101</v>
       </c>
       <c r="E13" s="1">
-        <v>0.0089950384572148323</v>
+        <v>0.010467460379004478</v>
       </c>
       <c r="F13" s="1">
-        <v>0.69804757833480835</v>
+        <v>0.33456981182098389</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.34896913170814514</v>
+        <v>-0.010100577026605606</v>
       </c>
       <c r="H13" s="1">
-        <v>0.89950382709503174</v>
+        <v>0.010467460379004478</v>
       </c>
       <c r="I13" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="J13" s="1">
-        <v>0.13657799839951221</v>
+        <v>0.13689916268645361</v>
       </c>
       <c r="K13" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -1181,34 +1112,34 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="1">
-        <v>-0.042419882911689001</v>
+        <v>-0.00036018214167749999</v>
       </c>
       <c r="E14" s="1">
-        <v>0.014573694206774235</v>
+        <v>0.00073013693327084184</v>
       </c>
       <c r="F14" s="1">
-        <v>0.0036060167476534843</v>
+        <v>0.62179523706436157</v>
       </c>
       <c r="G14" s="1">
-        <v>-4.2419881820678711</v>
+        <v>-0.00036018213722854853</v>
       </c>
       <c r="H14" s="1">
-        <v>1.457369327545166</v>
+        <v>0.00073013693327084184</v>
       </c>
       <c r="I14" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="J14" s="1">
-        <v>0.050708566313236503</v>
+        <v>0.0501799076404588</v>
       </c>
       <c r="K14" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -1216,34 +1147,34 @@
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
       </c>
       <c r="D15" s="1">
-        <v>-0.045477473080550203</v>
+        <v>-0.0002973660150791</v>
       </c>
       <c r="E15" s="1">
-        <v>0.01533137820661068</v>
+        <v>0.00074273592326790094</v>
       </c>
       <c r="F15" s="1">
-        <v>0.0030140592716634274</v>
+        <v>0.68888717889785767</v>
       </c>
       <c r="G15" s="1">
-        <v>-4.5477471351623535</v>
+        <v>-0.00029736600117757916</v>
       </c>
       <c r="H15" s="1">
-        <v>1.5331377983093262</v>
+        <v>0.00074273592326790094</v>
       </c>
       <c r="I15" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="J15" s="1">
-        <v>0.1371750438284183</v>
+        <v>0.1367983919803519</v>
       </c>
       <c r="K15" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16">
@@ -1251,34 +1182,34 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="1">
-        <v>0.22675722482199939</v>
+        <v>0.00017698291313080001</v>
       </c>
       <c r="E16" s="1">
-        <v>0.15968002378940582</v>
+        <v>0.00038902350934222341</v>
       </c>
       <c r="F16" s="1">
-        <v>0.15558655560016632</v>
+        <v>0.64915138483047485</v>
       </c>
       <c r="G16" s="1">
-        <v>22.675722122192383</v>
+        <v>0.00017698291048873216</v>
       </c>
       <c r="H16" s="1">
-        <v>15.968003273010254</v>
+        <v>0.00038902350934222341</v>
       </c>
       <c r="I16" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="J16" s="1">
-        <v>0.050487302002503197</v>
+        <v>0.050160190621734997</v>
       </c>
       <c r="K16" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -1286,104 +1217,34 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17" s="1">
-        <v>0.21190825069328101</v>
+        <v>9.2109628446899997e-05</v>
       </c>
       <c r="E17" s="1">
-        <v>0.16158725321292877</v>
+        <v>0.00040684995474293828</v>
       </c>
       <c r="F17" s="1">
-        <v>0.18971697986125946</v>
+        <v>0.82089263200759888</v>
       </c>
       <c r="G17" s="1">
-        <v>21.190824508666992</v>
+        <v>9.2109628894831985e-05</v>
       </c>
       <c r="H17" s="1">
-        <v>16.158725738525391</v>
+        <v>0.00040684995474293828</v>
       </c>
       <c r="I17" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="J17" s="1">
-        <v>0.1368186994635541</v>
+        <v>0.1367687308237551</v>
       </c>
       <c r="K17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="1">
-        <v>-0.081286499994409303</v>
-      </c>
-      <c r="E18" s="1">
-        <v>0.21086639165878296</v>
-      </c>
-      <c r="F18" s="1">
-        <v>0.69987577199935913</v>
-      </c>
-      <c r="G18" s="1">
-        <v>-8.1286497116088867</v>
-      </c>
-      <c r="H18" s="1">
-        <v>21.086639404296875</v>
-      </c>
-      <c r="I18" s="1">
-        <v>7467</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0.050237670407932998</v>
-      </c>
-      <c r="K18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="1">
-        <v>-0.055267916639279997</v>
-      </c>
-      <c r="E19" s="1">
-        <v>0.21200726926326752</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0.79433250427246094</v>
-      </c>
-      <c r="G19" s="1">
-        <v>-5.5267915725708008</v>
-      </c>
-      <c r="H19" s="1">
-        <v>21.200725555419922</v>
-      </c>
-      <c r="I19" s="1">
-        <v>7412</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0.13657009619706531</v>
-      </c>
-      <c r="K19" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1392,7 +1253,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1420,19 +1281,19 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E2" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="F2" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="3">
@@ -1440,19 +1301,19 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E3" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="F3" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="4">
@@ -1460,13 +1321,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E4" s="1">
         <v>7503</v>
@@ -1480,19 +1341,19 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E5" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="F5" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="6">
@@ -1500,19 +1361,19 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="F6" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="7">
@@ -1520,19 +1381,19 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="F7" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="8">
@@ -1540,19 +1401,19 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E8" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="F8" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="9">
@@ -1560,39 +1421,19 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
         <v>45</v>
       </c>
-      <c r="C9" t="s">
-        <v>61</v>
-      </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="F9" s="1">
-        <v>7412</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" s="1">
-        <v>7467</v>
-      </c>
-      <c r="F10" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
   </sheetData>
@@ -1601,7 +1442,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1609,13 +1450,13 @@
         <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
@@ -1653,43 +1494,43 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G2" s="1">
-        <v>0.0016488485153366001</v>
+        <v>-1.9623510208399999e-06</v>
       </c>
       <c r="H2" s="1">
-        <v>0.025536911562085152</v>
+        <v>9.3473554443335161e-06</v>
       </c>
       <c r="I2" s="1">
-        <v>0.94851857423782349</v>
+        <v>0.8337172269821167</v>
       </c>
       <c r="J2" s="1">
-        <v>0.16488485038280487</v>
+        <v>-1.9623510070232442e-06</v>
       </c>
       <c r="K2" s="1">
-        <v>2.5536911487579346</v>
+        <v>9.3473554443335161e-06</v>
       </c>
       <c r="L2" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M2" s="1">
-        <v>0.0513954480765864</v>
+        <v>0.050767203651670902</v>
       </c>
       <c r="N2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -1697,43 +1538,43 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G3" s="1">
-        <v>-0.1121860324342238</v>
+        <v>-1.6070496323899999e-05</v>
       </c>
       <c r="H3" s="1">
-        <v>0.097083844244480133</v>
+        <v>2.6586714739096351e-05</v>
       </c>
       <c r="I3" s="1">
-        <v>0.24786193668842316</v>
+        <v>0.54554057121276856</v>
       </c>
       <c r="J3" s="1">
-        <v>-11.218603134155273</v>
+        <v>-1.6070496712927707e-05</v>
       </c>
       <c r="K3" s="1">
-        <v>9.7083845138549805</v>
+        <v>2.6586714739096351e-05</v>
       </c>
       <c r="L3" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M3" s="1">
-        <v>0.0513954480765864</v>
+        <v>0.050767203651670902</v>
       </c>
       <c r="N3" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
@@ -1741,43 +1582,43 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G4" s="1">
-        <v>0.022136850500604301</v>
+        <v>-4.4452320782700001e-06</v>
       </c>
       <c r="H4" s="1">
-        <v>0.02920273132622242</v>
+        <v>1.0003863280871883e-05</v>
       </c>
       <c r="I4" s="1">
-        <v>0.44842678308486938</v>
+        <v>0.65678846836090088</v>
       </c>
       <c r="J4" s="1">
-        <v>2.2136850357055664</v>
+        <v>-4.4452322072174866e-06</v>
       </c>
       <c r="K4" s="1">
-        <v>2.9202730655670166</v>
+        <v>1.0003863280871883e-05</v>
       </c>
       <c r="L4" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M4" s="1">
-        <v>0.13878727984098449</v>
+        <v>0.13862350428243561</v>
       </c>
       <c r="N4" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
@@ -1785,43 +1626,43 @@
         <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G5" s="1">
-        <v>-0.198551424117964</v>
+        <v>-2.6510050885900001e-05</v>
       </c>
       <c r="H5" s="1">
-        <v>0.11751101911067963</v>
+        <v>3.377970278961584e-05</v>
       </c>
       <c r="I5" s="1">
-        <v>0.091096676886081696</v>
+        <v>0.43257534503936768</v>
       </c>
       <c r="J5" s="1">
-        <v>-19.855142593383789</v>
+        <v>-2.6510051611694507e-05</v>
       </c>
       <c r="K5" s="1">
-        <v>11.751102447509766</v>
+        <v>3.377970278961584e-05</v>
       </c>
       <c r="L5" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M5" s="1">
-        <v>0.13878727984098449</v>
+        <v>0.13862350428243561</v>
       </c>
       <c r="N5" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -1829,43 +1670,43 @@
         <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G6" s="1">
-        <v>1.9441728553525051</v>
+        <v>-0.021770601906866499</v>
       </c>
       <c r="H6" s="1">
-        <v>1.7547482252120972</v>
+        <v>0.021476367488503456</v>
       </c>
       <c r="I6" s="1">
-        <v>0.26788350939750671</v>
+        <v>0.31072574853897095</v>
       </c>
       <c r="J6" s="1">
-        <v>194.41728210449219</v>
+        <v>-0.021770602092146874</v>
       </c>
       <c r="K6" s="1">
-        <v>175.47482299804688</v>
+        <v>0.021476367488503456</v>
       </c>
       <c r="L6" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M6" s="1">
-        <v>0.050579234302893301</v>
+        <v>0.050778427780586499</v>
       </c>
       <c r="N6" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -1873,43 +1714,43 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G7" s="1">
-        <v>-6.8517482112603636</v>
+        <v>0.038260215208165402</v>
       </c>
       <c r="H7" s="1">
-        <v>7.5522332191467285</v>
+        <v>0.082579053938388825</v>
       </c>
       <c r="I7" s="1">
-        <v>0.36427569389343262</v>
+        <v>0.64313769340515137</v>
       </c>
       <c r="J7" s="1">
-        <v>-685.1748046875</v>
+        <v>0.038260214030742645</v>
       </c>
       <c r="K7" s="1">
-        <v>755.22332763671875</v>
+        <v>0.082579053938388825</v>
       </c>
       <c r="L7" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M7" s="1">
-        <v>0.050579234302893301</v>
+        <v>0.050778427780586499</v>
       </c>
       <c r="N7" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1917,43 +1758,43 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
         <v>5</v>
       </c>
       <c r="D8" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G8" s="1">
-        <v>3.7204612117351452</v>
+        <v>-0.050139812740084798</v>
       </c>
       <c r="H8" s="1">
-        <v>2.3515491485595703</v>
+        <v>0.023377209901809692</v>
       </c>
       <c r="I8" s="1">
-        <v>0.11361941695213318</v>
+        <v>0.031967572867870331</v>
       </c>
       <c r="J8" s="1">
-        <v>372.04611206054688</v>
+        <v>-0.050139810889959335</v>
       </c>
       <c r="K8" s="1">
-        <v>235.1549072265625</v>
+        <v>0.023377209901809692</v>
       </c>
       <c r="L8" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M8" s="1">
-        <v>0.13823649263226559</v>
+        <v>0.13887656070653789</v>
       </c>
       <c r="N8" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -1961,43 +1802,43 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G9" s="1">
-        <v>-10.84751235513289</v>
+        <v>0.1018500141602616</v>
       </c>
       <c r="H9" s="1">
-        <v>10.179479598999023</v>
+        <v>0.10464948415756226</v>
       </c>
       <c r="I9" s="1">
-        <v>0.2865929901599884</v>
+        <v>0.33042952418327332</v>
       </c>
       <c r="J9" s="1">
-        <v>-1084.751220703125</v>
+        <v>0.10185001045465469</v>
       </c>
       <c r="K9" s="1">
-        <v>1017.9479370117188</v>
+        <v>0.10464948415756226</v>
       </c>
       <c r="L9" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M9" s="1">
-        <v>0.13823649263226559</v>
+        <v>0.13887656070653789</v>
       </c>
       <c r="N9" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -2005,43 +1846,43 @@
         <v>31</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G10" s="1">
-        <v>0.0026944253084726002</v>
+        <v>-0.0099408707810950993</v>
       </c>
       <c r="H10" s="1">
-        <v>0.009645998477935791</v>
+        <v>0.025077709928154945</v>
       </c>
       <c r="I10" s="1">
-        <v>0.77999091148376465</v>
+        <v>0.69180798530578613</v>
       </c>
       <c r="J10" s="1">
-        <v>0.26944252848625183</v>
+        <v>-0.00994087103754282</v>
       </c>
       <c r="K10" s="1">
-        <v>0.96459978818893433</v>
+        <v>0.025077709928154945</v>
       </c>
       <c r="L10" s="1">
         <v>7503</v>
       </c>
       <c r="M10" s="1">
-        <v>0.0507462546846753</v>
+        <v>0.050899112910039103</v>
       </c>
       <c r="N10" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
@@ -2049,43 +1890,43 @@
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G11" s="1">
-        <v>-0.034647896137551398</v>
+        <v>-0.0471059136239423</v>
       </c>
       <c r="H11" s="1">
-        <v>0.032831646502017975</v>
+        <v>0.089230038225650787</v>
       </c>
       <c r="I11" s="1">
-        <v>0.29127895832061768</v>
+        <v>0.59755802154541016</v>
       </c>
       <c r="J11" s="1">
-        <v>-3.464789628982544</v>
+        <v>-0.047105912119150162</v>
       </c>
       <c r="K11" s="1">
-        <v>3.2831647396087647</v>
+        <v>0.089230038225650787</v>
       </c>
       <c r="L11" s="1">
         <v>7503</v>
       </c>
       <c r="M11" s="1">
-        <v>0.0507462546846753</v>
+        <v>0.050899112910039103</v>
       </c>
       <c r="N11" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -2093,43 +1934,43 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G12" s="1">
-        <v>-0.00072208760878209998</v>
+        <v>-0.029919418613095002</v>
       </c>
       <c r="H12" s="1">
-        <v>0.011348498985171318</v>
+        <v>0.028063053265213966</v>
       </c>
       <c r="I12" s="1">
-        <v>0.94926607608795166</v>
+        <v>0.28635594248771667</v>
       </c>
       <c r="J12" s="1">
-        <v>-0.072208762168884277</v>
+        <v>-0.029919419437646866</v>
       </c>
       <c r="K12" s="1">
-        <v>1.1348499059677124</v>
+        <v>0.028063053265213966</v>
       </c>
       <c r="L12" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M12" s="1">
-        <v>0.13816978281372311</v>
+        <v>0.13877017811521949</v>
       </c>
       <c r="N12" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
@@ -2137,43 +1978,43 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G13" s="1">
-        <v>-0.030884433706839201</v>
+        <v>0.0082210573076050997</v>
       </c>
       <c r="H13" s="1">
-        <v>0.040014788508415222</v>
+        <v>0.13620792329311371</v>
       </c>
       <c r="I13" s="1">
-        <v>0.44021779298782349</v>
+        <v>0.95187157392501831</v>
       </c>
       <c r="J13" s="1">
-        <v>-3.0884432792663574</v>
+        <v>0.0082210572436451912</v>
       </c>
       <c r="K13" s="1">
-        <v>4.0014786720275879</v>
+        <v>0.13620792329311371</v>
       </c>
       <c r="L13" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M13" s="1">
-        <v>0.13816978281372311</v>
+        <v>0.13877017811521949</v>
       </c>
       <c r="N13" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14">
@@ -2181,43 +2022,43 @@
         <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G14" s="1">
-        <v>1.2288076836856889</v>
+        <v>0.0018482693857592</v>
       </c>
       <c r="H14" s="1">
-        <v>1.2323294878005981</v>
+        <v>0.0076680225320160389</v>
       </c>
       <c r="I14" s="1">
-        <v>0.31869548559188843</v>
+        <v>0.80952721834182739</v>
       </c>
       <c r="J14" s="1">
-        <v>122.88076782226563</v>
+        <v>0.0018482693703845143</v>
       </c>
       <c r="K14" s="1">
-        <v>123.23294067382813</v>
+        <v>0.0076680225320160389</v>
       </c>
       <c r="L14" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M14" s="1">
-        <v>0.051205940202533398</v>
+        <v>0.051438925781112803</v>
       </c>
       <c r="N14" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -2225,43 +2066,43 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
         <v>4</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E15" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F15" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G15" s="1">
-        <v>-0.82700216620814648</v>
+        <v>-0.045888680557933201</v>
       </c>
       <c r="H15" s="1">
-        <v>4.6975569725036621</v>
+        <v>0.033185016363859177</v>
       </c>
       <c r="I15" s="1">
-        <v>0.86025512218475342</v>
+        <v>0.16672214865684509</v>
       </c>
       <c r="J15" s="1">
-        <v>-82.700218200683594</v>
+        <v>-0.045888680964708328</v>
       </c>
       <c r="K15" s="1">
-        <v>469.75570678710938</v>
+        <v>0.033185016363859177</v>
       </c>
       <c r="L15" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M15" s="1">
-        <v>0.051205940202533398</v>
+        <v>0.051438925781112803</v>
       </c>
       <c r="N15" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -2269,43 +2110,43 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F16" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16" s="1">
+        <v>-0.00062708452503150002</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.0083588259294629097</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.94019830226898193</v>
+      </c>
+      <c r="J16" s="1">
+        <v>-0.00062708451878279448</v>
+      </c>
+      <c r="K16" s="1">
+        <v>0.0083588259294629097</v>
+      </c>
+      <c r="L16" s="1">
+        <v>7448</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0.138753643762112</v>
+      </c>
+      <c r="N16" t="s">
         <v>87</v>
-      </c>
-      <c r="G16" s="1">
-        <v>2.1858622150751401</v>
-      </c>
-      <c r="H16" s="1">
-        <v>1.1581724882125854</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0.059114966541528702</v>
-      </c>
-      <c r="J16" s="1">
-        <v>218.58622741699219</v>
-      </c>
-      <c r="K16" s="1">
-        <v>115.81725311279297</v>
-      </c>
-      <c r="L16" s="1">
-        <v>7412</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0.13875142445007621</v>
-      </c>
-      <c r="N16" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="17">
@@ -2313,43 +2154,43 @@
         <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="1">
+        <v>-0.032234899612756801</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.042506325989961624</v>
+      </c>
+      <c r="I17" s="1">
+        <v>0.44823828339576721</v>
+      </c>
+      <c r="J17" s="1">
+        <v>-0.032234899699687958</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0.042506325989961624</v>
+      </c>
+      <c r="L17" s="1">
+        <v>7448</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0.138753643762112</v>
+      </c>
+      <c r="N17" t="s">
         <v>88</v>
-      </c>
-      <c r="G17" s="1">
-        <v>-4.4050627680517645</v>
-      </c>
-      <c r="H17" s="1">
-        <v>4.9523167610168457</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0.3737369179725647</v>
-      </c>
-      <c r="J17" s="1">
-        <v>-440.50628662109375</v>
-      </c>
-      <c r="K17" s="1">
-        <v>495.231689453125</v>
-      </c>
-      <c r="L17" s="1">
-        <v>7412</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0.13875142445007621</v>
-      </c>
-      <c r="N17" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="18">
@@ -2357,43 +2198,43 @@
         <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G18" s="1">
-        <v>-0.63137277326861863</v>
+        <v>-0.001643070809533</v>
       </c>
       <c r="H18" s="1">
-        <v>0.30760154128074646</v>
+        <v>0.004682544618844986</v>
       </c>
       <c r="I18" s="1">
-        <v>0.040114596486091614</v>
+        <v>0.72566884756088257</v>
       </c>
       <c r="J18" s="1">
-        <v>-63.137275695800781</v>
+        <v>-0.0016430708346888423</v>
       </c>
       <c r="K18" s="1">
-        <v>30.760154724121094</v>
+        <v>0.004682544618844986</v>
       </c>
       <c r="L18" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M18" s="1">
-        <v>0.050894061439361801</v>
+        <v>0.051097865553086298</v>
       </c>
       <c r="N18" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
@@ -2401,43 +2242,43 @@
         <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
         <v>4</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F19" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G19" s="1">
-        <v>2.190151337362344</v>
+        <v>-0.026383823475306701</v>
       </c>
       <c r="H19" s="1">
-        <v>1.0763565301895142</v>
+        <v>0.015763867646455765</v>
       </c>
       <c r="I19" s="1">
-        <v>0.041872762143611908</v>
+        <v>0.094191588461399078</v>
       </c>
       <c r="J19" s="1">
-        <v>219.01513671875</v>
+        <v>-0.026383822783827782</v>
       </c>
       <c r="K19" s="1">
-        <v>107.63565063476563</v>
+        <v>0.015763867646455765</v>
       </c>
       <c r="L19" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M19" s="1">
-        <v>0.050894061439361801</v>
+        <v>0.051097865553086298</v>
       </c>
       <c r="N19" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20">
@@ -2445,43 +2286,43 @@
         <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
       </c>
       <c r="D20" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E20" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G20" s="1">
-        <v>-0.73256467863884178</v>
+        <v>-0.0020471372137087001</v>
       </c>
       <c r="H20" s="1">
-        <v>0.26996034383773804</v>
+        <v>0.0054405885748565197</v>
       </c>
       <c r="I20" s="1">
-        <v>0.0066556287929415703</v>
+        <v>0.70671522617340088</v>
       </c>
       <c r="J20" s="1">
-        <v>-73.2564697265625</v>
+        <v>-0.0020471371244639158</v>
       </c>
       <c r="K20" s="1">
-        <v>26.996036529541016</v>
+        <v>0.0054405885748565197</v>
       </c>
       <c r="L20" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M20" s="1">
-        <v>0.13847736379198239</v>
+        <v>0.13859897114285411</v>
       </c>
       <c r="N20" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
@@ -2489,43 +2330,43 @@
         <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
         <v>5</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G21" s="1">
-        <v>2.591817718479096</v>
+        <v>-0.025628694095252602</v>
       </c>
       <c r="H21" s="1">
-        <v>1.1443439722061157</v>
+        <v>0.026386862620711327</v>
       </c>
       <c r="I21" s="1">
-        <v>0.02351919561624527</v>
+        <v>0.33141526579856873</v>
       </c>
       <c r="J21" s="1">
-        <v>259.1817626953125</v>
+        <v>-0.025628693401813507</v>
       </c>
       <c r="K21" s="1">
-        <v>114.43440246582031</v>
+        <v>0.026386862620711327</v>
       </c>
       <c r="L21" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M21" s="1">
-        <v>0.13847736379198239</v>
+        <v>0.13859897114285411</v>
       </c>
       <c r="N21" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22">
@@ -2533,43 +2374,43 @@
         <v>34</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
         <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E22" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F22" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G22" s="1">
-        <v>-0.0116181176354768</v>
+        <v>-0.036955462163328498</v>
       </c>
       <c r="H22" s="1">
-        <v>0.024774229153990746</v>
+        <v>0.027329010888934135</v>
       </c>
       <c r="I22" s="1">
-        <v>0.63909834623336792</v>
+        <v>0.1762976199388504</v>
       </c>
       <c r="J22" s="1">
-        <v>-1.1618117094039917</v>
+        <v>-0.036955460906028748</v>
       </c>
       <c r="K22" s="1">
-        <v>2.4774229526519775</v>
+        <v>0.027329010888934135</v>
       </c>
       <c r="L22" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M22" s="1">
-        <v>0.0512759201618549</v>
+        <v>0.050838747555215301</v>
       </c>
       <c r="N22" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23">
@@ -2577,43 +2418,43 @@
         <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
       </c>
       <c r="D23" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G23" s="1">
-        <v>-0.073159670234789198</v>
+        <v>0.1955340826910926</v>
       </c>
       <c r="H23" s="1">
-        <v>0.097016230225563049</v>
+        <v>0.096046485006809235</v>
       </c>
       <c r="I23" s="1">
-        <v>0.45079085230827332</v>
+        <v>0.041767675429582596</v>
       </c>
       <c r="J23" s="1">
-        <v>-7.3159670829772949</v>
+        <v>0.19553408026695251</v>
       </c>
       <c r="K23" s="1">
-        <v>9.7016229629516602</v>
+        <v>0.096046485006809235</v>
       </c>
       <c r="L23" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M23" s="1">
-        <v>0.0512759201618549</v>
+        <v>0.050838747555215301</v>
       </c>
       <c r="N23" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24">
@@ -2621,43 +2462,43 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" t="s">
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G24" s="1">
-        <v>-0.026054710273132602</v>
+        <v>-0.019538891951111099</v>
       </c>
       <c r="H24" s="1">
-        <v>0.024450471624732018</v>
+        <v>0.040562309324741364</v>
       </c>
       <c r="I24" s="1">
-        <v>0.28659918904304504</v>
+        <v>0.63001859188079834</v>
       </c>
       <c r="J24" s="1">
-        <v>-2.605471134185791</v>
+        <v>-0.019538892433047295</v>
       </c>
       <c r="K24" s="1">
-        <v>2.44504714012146</v>
+        <v>0.040562309324741364</v>
       </c>
       <c r="L24" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M24" s="1">
-        <v>0.13910930352431111</v>
+        <v>0.13846905944262669</v>
       </c>
       <c r="N24" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25">
@@ -2665,43 +2506,43 @@
         <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" t="s">
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G25" s="1">
-        <v>-0.068439670645898398</v>
+        <v>0.089866384897878293</v>
       </c>
       <c r="H25" s="1">
-        <v>0.094213567674160004</v>
+        <v>0.16813910007476807</v>
       </c>
       <c r="I25" s="1">
-        <v>0.46757450699806213</v>
+        <v>0.59301197528839111</v>
       </c>
       <c r="J25" s="1">
-        <v>-6.8439669609069824</v>
+        <v>0.089866384863853455</v>
       </c>
       <c r="K25" s="1">
-        <v>9.4213571548461914</v>
+        <v>0.16813910007476807</v>
       </c>
       <c r="L25" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M25" s="1">
-        <v>0.13910930352431111</v>
+        <v>0.13846905944262669</v>
       </c>
       <c r="N25" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26">
@@ -2709,43 +2550,43 @@
         <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
         <v>4</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G26" s="1">
-        <v>-0.022917755302006199</v>
+        <v>-0.00012621219774749999</v>
       </c>
       <c r="H26" s="1">
-        <v>0.092235319316387177</v>
+        <v>0.0019272579811513424</v>
       </c>
       <c r="I26" s="1">
-        <v>0.80377042293548584</v>
+        <v>0.94778549671173096</v>
       </c>
       <c r="J26" s="1">
-        <v>-2.2917754650115967</v>
+        <v>-0.0001262121950276196</v>
       </c>
       <c r="K26" s="1">
-        <v>9.2235317230224609</v>
+        <v>0.0019272579811513424</v>
       </c>
       <c r="L26" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M26" s="1">
-        <v>0.0507510830981883</v>
+        <v>0.050465496955577803</v>
       </c>
       <c r="N26" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27">
@@ -2753,43 +2594,43 @@
         <v>35</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
       </c>
       <c r="D27" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E27" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G27" s="1">
-        <v>0.113044476665029</v>
+        <v>0.0025251387113275998</v>
       </c>
       <c r="H27" s="1">
-        <v>0.26968473196029663</v>
+        <v>0.0068870964460074902</v>
       </c>
       <c r="I27" s="1">
-        <v>0.67508989572525025</v>
+        <v>0.7138817310333252</v>
       </c>
       <c r="J27" s="1">
-        <v>11.304448127746582</v>
+        <v>0.0025251386687159538</v>
       </c>
       <c r="K27" s="1">
-        <v>26.968471527099609</v>
+        <v>0.0068870964460074902</v>
       </c>
       <c r="L27" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M27" s="1">
-        <v>0.0507510830981883</v>
+        <v>0.050465496955577803</v>
       </c>
       <c r="N27" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -2797,43 +2638,43 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C28" t="s">
         <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G28" s="1">
-        <v>-0.0050021754195777</v>
+        <v>0.0021778720559203998</v>
       </c>
       <c r="H28" s="1">
-        <v>0.09884198009967804</v>
+        <v>0.0022206190042197704</v>
       </c>
       <c r="I28" s="1">
-        <v>0.95963805913925171</v>
+        <v>0.32671603560447693</v>
       </c>
       <c r="J28" s="1">
-        <v>-0.50021755695343018</v>
+        <v>0.0021778719965368509</v>
       </c>
       <c r="K28" s="1">
-        <v>9.8841981887817383</v>
+        <v>0.0022206190042197704</v>
       </c>
       <c r="L28" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M28" s="1">
-        <v>0.13791313465708399</v>
+        <v>0.13862826191552169</v>
       </c>
       <c r="N28" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -2841,43 +2682,43 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C29" t="s">
         <v>5</v>
       </c>
       <c r="D29" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F29" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G29" s="1">
-        <v>0.0083360061851005998</v>
+        <v>-0.010785576952603199</v>
       </c>
       <c r="H29" s="1">
-        <v>0.31785258650779724</v>
+        <v>0.0095417508855462074</v>
       </c>
       <c r="I29" s="1">
-        <v>0.97907704114913941</v>
+        <v>0.25832617282867432</v>
       </c>
       <c r="J29" s="1">
-        <v>0.83360064029693604</v>
+        <v>-0.010785576887428761</v>
       </c>
       <c r="K29" s="1">
-        <v>31.785257339477539</v>
+        <v>0.0095417508855462074</v>
       </c>
       <c r="L29" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M29" s="1">
-        <v>0.13791313465708399</v>
+        <v>0.13862826191552169</v>
       </c>
       <c r="N29" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30">
@@ -2885,43 +2726,43 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F30" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G30" s="1">
-        <v>-0.46743694799884528</v>
+        <v>0.00053582688855600004</v>
       </c>
       <c r="H30" s="1">
-        <v>0.43690803647041321</v>
+        <v>0.00082172662951052189</v>
       </c>
       <c r="I30" s="1">
-        <v>0.28467559814453125</v>
+        <v>0.51435315608978272</v>
       </c>
       <c r="J30" s="1">
-        <v>-46.743694305419922</v>
+        <v>0.00053582689724862576</v>
       </c>
       <c r="K30" s="1">
-        <v>43.690803527832031</v>
+        <v>0.00082172662951052189</v>
       </c>
       <c r="L30" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M30" s="1">
-        <v>0.052040561772501298</v>
+        <v>0.050439471687052102</v>
       </c>
       <c r="N30" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
@@ -2929,43 +2770,43 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C31" t="s">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E31" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G31" s="1">
-        <v>-1.724957658362168</v>
+        <v>-0.0028051735311216998</v>
       </c>
       <c r="H31" s="1">
-        <v>1.4567935466766358</v>
+        <v>0.0033067911863327026</v>
       </c>
       <c r="I31" s="1">
-        <v>0.23638206720352173</v>
+        <v>0.39626714587211609</v>
       </c>
       <c r="J31" s="1">
-        <v>-172.49577331542969</v>
+        <v>-0.0028051736298948526</v>
       </c>
       <c r="K31" s="1">
-        <v>145.67935180664063</v>
+        <v>0.0033067911863327026</v>
       </c>
       <c r="L31" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="M31" s="1">
-        <v>0.052040561772501298</v>
+        <v>0.050439471687052102</v>
       </c>
       <c r="N31" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
     </row>
     <row r="32">
@@ -2973,43 +2814,43 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" t="s">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F32" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G32" s="1">
-        <v>-0.45901723853430759</v>
+        <v>-0.00083033332328750001</v>
       </c>
       <c r="H32" s="1">
-        <v>0.42072498798370361</v>
+        <v>0.001103205606341362</v>
       </c>
       <c r="I32" s="1">
-        <v>0.27526631951332092</v>
+        <v>0.45165720582008362</v>
       </c>
       <c r="J32" s="1">
-        <v>-45.901721954345703</v>
+        <v>-0.00083033333066850901</v>
       </c>
       <c r="K32" s="1">
-        <v>42.072498321533203</v>
+        <v>0.001103205606341362</v>
       </c>
       <c r="L32" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M32" s="1">
-        <v>0.13937554740710209</v>
+        <v>0.1384952519905063</v>
       </c>
       <c r="N32" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33">
@@ -3017,219 +2858,43 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
         <v>5</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E33" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="F33" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="G33" s="1">
-        <v>-2.5278873291690061</v>
+        <v>0.0030854890376165998</v>
       </c>
       <c r="H33" s="1">
-        <v>1.4209482669830322</v>
+        <v>0.0045895297080278397</v>
       </c>
       <c r="I33" s="1">
-        <v>0.07523740828037262</v>
+        <v>0.5013999342918396</v>
       </c>
       <c r="J33" s="1">
-        <v>-252.78872680664063</v>
+        <v>0.0030854891519993544</v>
       </c>
       <c r="K33" s="1">
-        <v>142.09481811523438</v>
+        <v>0.0045895297080278397</v>
       </c>
       <c r="L33" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
       <c r="M33" s="1">
-        <v>0.13937554740710209</v>
+        <v>0.1384952519905063</v>
       </c>
       <c r="N33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" t="s">
-        <v>4</v>
-      </c>
-      <c r="D34" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" t="s">
-        <v>85</v>
-      </c>
-      <c r="F34" t="s">
-        <v>87</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0.0010056474240231999</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0.98150467872619629</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0.99918246269226074</v>
-      </c>
-      <c r="J34" s="1">
-        <v>0.10056474059820175</v>
-      </c>
-      <c r="K34" s="1">
-        <v>98.150466918945313</v>
-      </c>
-      <c r="L34" s="1">
-        <v>7467</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0.050618629318548797</v>
-      </c>
-      <c r="N34" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" t="s">
-        <v>68</v>
-      </c>
-      <c r="E35" t="s">
-        <v>86</v>
-      </c>
-      <c r="F35" t="s">
-        <v>88</v>
-      </c>
-      <c r="G35" s="1">
-        <v>2.031552279511629</v>
-      </c>
-      <c r="H35" s="1">
-        <v>4.198758602142334</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0.62849521636962891</v>
-      </c>
-      <c r="J35" s="1">
-        <v>203.15522766113281</v>
-      </c>
-      <c r="K35" s="1">
-        <v>419.8758544921875</v>
-      </c>
-      <c r="L35" s="1">
-        <v>7467</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0.050618629318548797</v>
-      </c>
-      <c r="N35" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" t="s">
-        <v>85</v>
-      </c>
-      <c r="F36" t="s">
-        <v>87</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0.25545761040322712</v>
-      </c>
-      <c r="H36" s="1">
-        <v>1.0005459785461426</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0.79847735166549683</v>
-      </c>
-      <c r="J36" s="1">
-        <v>25.545761108398438</v>
-      </c>
-      <c r="K36" s="1">
-        <v>100.05459594726563</v>
-      </c>
-      <c r="L36" s="1">
-        <v>7412</v>
-      </c>
-      <c r="M36" s="1">
-        <v>0.13812263410496989</v>
-      </c>
-      <c r="N36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" t="s">
-        <v>88</v>
-      </c>
-      <c r="G37" s="1">
-        <v>1.468969084816425</v>
-      </c>
-      <c r="H37" s="1">
-        <v>3.9422404766082764</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0.70942914485931396</v>
-      </c>
-      <c r="J37" s="1">
-        <v>146.89691162109375</v>
-      </c>
-      <c r="K37" s="1">
-        <v>394.22402954101563</v>
-      </c>
-      <c r="L37" s="1">
-        <v>7412</v>
-      </c>
-      <c r="M37" s="1">
-        <v>0.13812263410496989</v>
-      </c>
-      <c r="N37" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3238,7 +2903,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3246,19 +2911,19 @@
         <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="E1" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="F1" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="G1" t="s">
         <v>26</v>
@@ -3272,25 +2937,25 @@
         <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="G2" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="H2" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="3">
@@ -3298,25 +2963,25 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="G3" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="H3" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="4">
@@ -3324,25 +2989,25 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="G4" s="1">
         <v>7503</v>
       </c>
       <c r="H4" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="5">
@@ -3350,25 +3015,25 @@
         <v>32</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G5" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="H5" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="6">
@@ -3376,25 +3041,25 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="F6" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="G6" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="H6" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="7">
@@ -3402,25 +3067,25 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="E7" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="F7" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="G7" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="H7" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="8">
@@ -3428,25 +3093,25 @@
         <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="H8" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
     <row r="9">
@@ -3454,51 +3119,25 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="G9" s="1">
-        <v>7467</v>
+        <v>7503</v>
       </c>
       <c r="H9" s="1">
-        <v>7412</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" t="s">
-        <v>122</v>
-      </c>
-      <c r="E10" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" t="s">
-        <v>124</v>
-      </c>
-      <c r="G10" s="1">
-        <v>7467</v>
-      </c>
-      <c r="H10" s="1">
-        <v>7412</v>
+        <v>7448</v>
       </c>
     </row>
   </sheetData>
